--- a/тпр2.xlsx
+++ b/тпр2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3-МД-4 ПИ\Малыгина Елизавета\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321F554D-A20B-4CA1-8506-839C0DFEA150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D618F5F3-AE74-4C7D-B05C-4E44C3DF225B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,7 +601,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.625" customWidth="1"/>
     <col min="3" max="3" width="24.875" customWidth="1"/>
@@ -614,7 +614,7 @@
     <col min="10" max="10" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -646,39 +646,39 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -710,7 +710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -742,7 +742,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -774,7 +774,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -806,7 +806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -838,7 +838,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -870,7 +870,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -902,7 +902,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -934,7 +934,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -966,7 +966,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -998,7 +998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>44</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>51</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>53</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -1638,32 +1638,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I33" s="2" t="s">
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="J33" s="3" t="s">
